--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,61 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105034634</v>
+        <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>58817</v>
+        <v>83486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Namnlös nära Danasjö, Ly lm</t>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571884</v>
+        <v>571741</v>
       </c>
       <c r="R2" t="n">
-        <v>7267847</v>
+        <v>7267648</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +759,2323 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270597</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137270594</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92144</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>571319</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7267744</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövrik gransumpskog vid myrkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270594</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137270589</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571535</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7267980</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270589</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137270592</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571862</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7267915</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270592</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137270576</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83371</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571858</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7267921</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270576</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137270578</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83499</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571533</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7268152</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270578</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137270593</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80619</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571759</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7268024</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270593</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137270579</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571945</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7267594</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270579</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137270580</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571664</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7267619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, medelåldrig granskog på blockig terräng</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270580</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137270583</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571313</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7267784</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, äldre granskog på blockig terräng</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270583</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137270587</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571532</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7268149</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270587</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137270588</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83494</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571282</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7267594</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Medelåldrig, lövrik blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270588</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137270590</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83494</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571649</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7267836</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, medelåldrig granskog på blockig terräng</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270590</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137270596</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83494</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571735</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7267653</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270596</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137270577</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80629</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571759</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7268024</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270577</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137270582</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571467</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7268118</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270582</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105034634</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Namnlös nära Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571884</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7267847</v>
+      </c>
+      <c r="S18" t="n">
+        <v>75</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Anders Forsgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Anders Forsgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Internationell Herptilinventering med Svensk bas</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105034634</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137270595</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78508</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571841</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7267936</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270595</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137270598</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78508</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571360</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7267876</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre, lövrik granskog i sluttning, naturskogsartad miljö</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270598</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137270591</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79582</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>864</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571968</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7267578</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270591</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137270585</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83371</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>571981</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7267592</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270585</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137270581</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83494</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästnäset, söder om Danasjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>571966</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7267579</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270581</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>137270582</v>
       </c>
       <c r="B17" t="n">
-        <v>5181</v>
+        <v>5187</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22873-2026 artfynd.xlsx
+++ b/artfynd/A 22873-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137270597</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137270594</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137270589</v>
       </c>
       <c r="B4" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137270592</v>
       </c>
       <c r="B5" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137270576</v>
       </c>
       <c r="B6" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137270578</v>
       </c>
       <c r="B7" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>137270593</v>
       </c>
       <c r="B8" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137270579</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137270580</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>137270583</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>137270587</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137270588</v>
       </c>
       <c r="B13" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137270590</v>
       </c>
       <c r="B14" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>137270596</v>
       </c>
       <c r="B15" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>137270577</v>
       </c>
       <c r="B16" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137270595</v>
       </c>
       <c r="B19" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137270598</v>
       </c>
       <c r="B20" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>137270591</v>
       </c>
       <c r="B21" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>137270585</v>
       </c>
       <c r="B22" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>137270581</v>
       </c>
       <c r="B23" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
